--- a/html/Sundhedscentersystemer_excel.XLSX
+++ b/html/Sundhedscentersystemer_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A71044E5-B201-43B6-9CE8-1911F83E05FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74C97CA4-9D5B-4CAB-9148-CEF82B0FBAED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30855" yWindow="1950" windowWidth="21600" windowHeight="11235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 19-12-2025" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 29-01-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sundhedscentersystemer">'Opdateret d. 19-12-2025'!$A$1:$J$14</definedName>
+    <definedName name="Sundhedscentersystemer">'Opdateret d. 29-01-2026'!$A$1:$J$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Sundhedscentersystemer_excel.XLSX
+++ b/html/Sundhedscentersystemer_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74C97CA4-9D5B-4CAB-9148-CEF82B0FBAED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A5DF138-C7A5-41EF-A5D8-20E915EDAEBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 29-01-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 02-02-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sundhedscentersystemer">'Opdateret d. 29-01-2026'!$A$1:$J$14</definedName>
+    <definedName name="Sundhedscentersystemer">'Opdateret d. 02-02-2026'!$A$1:$J$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Sundhedscentersystemer_excel.XLSX
+++ b/html/Sundhedscentersystemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A5DF138-C7A5-41EF-A5D8-20E915EDAEBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04966E19-FD01-44B2-B5F7-4500DCE9258E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 02-02-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 20-02-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sundhedscentersystemer">'Opdateret d. 02-02-2026'!$A$1:$J$14</definedName>
+    <definedName name="Sundhedscentersystemer">'Opdateret d. 20-02-2026'!$A$1:$J$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -461,9 +461,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J14"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -495,7 +495,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -527,7 +527,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>15</v>
       </c>
@@ -559,7 +559,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>17</v>
       </c>
@@ -591,7 +591,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>19</v>
       </c>
@@ -623,7 +623,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>21</v>
       </c>
@@ -655,7 +655,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>24</v>
       </c>
@@ -687,7 +687,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>24</v>
       </c>
@@ -719,7 +719,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>15</v>
       </c>
@@ -751,7 +751,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>17</v>
       </c>
@@ -783,7 +783,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>28</v>
       </c>
@@ -815,7 +815,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>19</v>
       </c>
@@ -847,7 +847,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>21</v>
       </c>
@@ -879,7 +879,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>30</v>
       </c>

--- a/html/Sundhedscentersystemer_excel.XLSX
+++ b/html/Sundhedscentersystemer_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04966E19-FD01-44B2-B5F7-4500DCE9258E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E58F914A-4FD7-4FC4-958D-E71CBFD19C20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 20-02-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 04-03-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sundhedscentersystemer">'Opdateret d. 20-02-2026'!$A$1:$J$14</definedName>
+    <definedName name="Sundhedscentersystemer">'Opdateret d. 04-03-2026'!$A$1:$J$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Sundhedscentersystemer_excel.XLSX
+++ b/html/Sundhedscentersystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E58F914A-4FD7-4FC4-958D-E71CBFD19C20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EFFE91B-7F68-4FC0-BB3F-BA3A0C93769F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 04-03-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 06-03-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sundhedscentersystemer">'Opdateret d. 04-03-2026'!$A$1:$J$14</definedName>
+    <definedName name="Sundhedscentersystemer">'Opdateret d. 06-03-2026'!$A$1:$J$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Sundhedscentersystemer_excel.XLSX
+++ b/html/Sundhedscentersystemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EFFE91B-7F68-4FC0-BB3F-BA3A0C93769F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FD23848-583E-424D-9171-F77D22220F36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Sundhedscentersystemer_excel.XLSX
+++ b/html/Sundhedscentersystemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FD23848-583E-424D-9171-F77D22220F36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82EFB0D5-6B66-414C-BDAD-65A150F2C169}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Sundhedscentersystemer_excel.XLSX
+++ b/html/Sundhedscentersystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82EFB0D5-6B66-414C-BDAD-65A150F2C169}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E2BADC4-1632-4D62-AF32-9DFA2B74CA48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14625" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 06-03-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 09-03-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sundhedscentersystemer">'Opdateret d. 06-03-2026'!$A$1:$J$14</definedName>
+    <definedName name="Sundhedscentersystemer">'Opdateret d. 09-03-2026'!$A$1:$J$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Sundhedscentersystemer_excel.XLSX
+++ b/html/Sundhedscentersystemer_excel.XLSX
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E2BADC4-1632-4D62-AF32-9DFA2B74CA48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0CF546C-C414-4FBD-86FD-ECA5DB64BF7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14625" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 09-03-2026" sheetId="1" r:id="rId1"/>

--- a/html/Sundhedscentersystemer_excel.XLSX
+++ b/html/Sundhedscentersystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0CF546C-C414-4FBD-86FD-ECA5DB64BF7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27CB6167-AF62-45C7-A539-49FDCCC2CCE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 09-03-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 11-03-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sundhedscentersystemer">'Opdateret d. 09-03-2026'!$A$1:$J$14</definedName>
+    <definedName name="Sundhedscentersystemer">'Opdateret d. 11-03-2026'!$A$1:$J$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Sundhedscentersystemer_excel.XLSX
+++ b/html/Sundhedscentersystemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27CB6167-AF62-45C7-A539-49FDCCC2CCE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFA663F3-47C5-4190-A446-D3B403CA7125}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Sundhedscentersystemer_excel.XLSX
+++ b/html/Sundhedscentersystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFA663F3-47C5-4190-A446-D3B403CA7125}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8B9BB4D-30B2-4910-AF7B-F6520948B0C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 11-03-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 20-03-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sundhedscentersystemer">'Opdateret d. 11-03-2026'!$A$1:$J$14</definedName>
+    <definedName name="Sundhedscentersystemer">'Opdateret d. 20-03-2026'!$A$1:$J$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Sundhedscentersystemer_excel.XLSX
+++ b/html/Sundhedscentersystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8B9BB4D-30B2-4910-AF7B-F6520948B0C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04B6FB07-8D9E-4DD0-9427-22D32E2BC251}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 20-03-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 25-03-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sundhedscentersystemer">'Opdateret d. 20-03-2026'!$A$1:$J$14</definedName>
+    <definedName name="Sundhedscentersystemer">'Opdateret d. 25-03-2026'!$A$1:$J$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Sundhedscentersystemer_excel.XLSX
+++ b/html/Sundhedscentersystemer_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04B6FB07-8D9E-4DD0-9427-22D32E2BC251}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E136F85-4E4D-4700-88F8-EAD3E4326614}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 25-03-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 08-04-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sundhedscentersystemer">'Opdateret d. 25-03-2026'!$A$1:$J$14</definedName>
+    <definedName name="Sundhedscentersystemer">'Opdateret d. 08-04-2026'!$A$1:$J$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Sundhedscentersystemer_excel.XLSX
+++ b/html/Sundhedscentersystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E136F85-4E4D-4700-88F8-EAD3E4326614}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA50058D-DDE0-4225-82FA-82533B3AE10B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 08-04-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 10-04-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sundhedscentersystemer">'Opdateret d. 08-04-2026'!$A$1:$J$14</definedName>
+    <definedName name="Sundhedscentersystemer">'Opdateret d. 10-04-2026'!$A$1:$J$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Sundhedscentersystemer_excel.XLSX
+++ b/html/Sundhedscentersystemer_excel.XLSX
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA50058D-DDE0-4225-82FA-82533B3AE10B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73DB9E65-1A90-4D05-992A-AFF269015753}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-15045" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 10-04-2026" sheetId="1" r:id="rId1"/>

--- a/html/Sundhedscentersystemer_excel.XLSX
+++ b/html/Sundhedscentersystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73DB9E65-1A90-4D05-992A-AFF269015753}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C40981F1-C259-4E30-8709-675799842E0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-15045" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 10-04-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 14-04-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sundhedscentersystemer">'Opdateret d. 10-04-2026'!$A$1:$J$14</definedName>
+    <definedName name="Sundhedscentersystemer">'Opdateret d. 14-04-2026'!$A$1:$J$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Sundhedscentersystemer_excel.XLSX
+++ b/html/Sundhedscentersystemer_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C40981F1-C259-4E30-8709-675799842E0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF8AF01D-7372-4006-BDA6-606979BA1EBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 14-04-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 24-04-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sundhedscentersystemer">'Opdateret d. 14-04-2026'!$A$1:$J$14</definedName>
+    <definedName name="Sundhedscentersystemer">'Opdateret d. 24-04-2026'!$A$1:$J$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Sundhedscentersystemer_excel.XLSX
+++ b/html/Sundhedscentersystemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF8AF01D-7372-4006-BDA6-606979BA1EBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CA1C522-197A-45C6-9443-F1C6E0A7C88A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -49,10 +49,10 @@
     <t>Rambøll Care (Rambøll)</t>
   </si>
   <si>
-    <t>Sundhed (Dedalus)</t>
-  </si>
-  <si>
-    <t>Topica (Dedalus)</t>
+    <t>Sundhed (Dedalus Healthcare Denmark)</t>
+  </si>
+  <si>
+    <t>Topica (Dedalus Healthcare Denmark)</t>
   </si>
   <si>
     <t>Negativ VANS kvittering</t>

--- a/html/Sundhedscentersystemer_excel.XLSX
+++ b/html/Sundhedscentersystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CA1C522-197A-45C6-9443-F1C6E0A7C88A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8019AC3E-1010-42CA-8B1E-78601FCC161E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 24-04-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 27-04-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sundhedscentersystemer">'Opdateret d. 24-04-2026'!$A$1:$J$14</definedName>
+    <definedName name="Sundhedscentersystemer">'Opdateret d. 27-04-2026'!$A$1:$J$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Sundhedscentersystemer_excel.XLSX
+++ b/html/Sundhedscentersystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8019AC3E-1010-42CA-8B1E-78601FCC161E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F00B1787-C23C-4F01-BEF1-F9601DCAC4A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="384" yWindow="384" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 27-04-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 06-05-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sundhedscentersystemer">'Opdateret d. 27-04-2026'!$A$1:$J$14</definedName>
+    <definedName name="Sundhedscentersystemer">'Opdateret d. 06-05-2026'!$A$1:$J$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Sundhedscentersystemer_excel.XLSX
+++ b/html/Sundhedscentersystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F00B1787-C23C-4F01-BEF1-F9601DCAC4A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A20137A0-F46B-452D-B315-1F36587D1386}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="384" yWindow="384" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 06-05-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 01-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sundhedscentersystemer">'Opdateret d. 06-05-2026'!$A$1:$J$14</definedName>
+    <definedName name="Sundhedscentersystemer">'Opdateret d. 01-06-2026'!$A$1:$J$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Sundhedscentersystemer_excel.XLSX
+++ b/html/Sundhedscentersystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A20137A0-F46B-452D-B315-1F36587D1386}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C903D9B-5306-40A9-BC0E-9BBC67F1605D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 01-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 02-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sundhedscentersystemer">'Opdateret d. 01-06-2026'!$A$1:$J$14</definedName>
+    <definedName name="Sundhedscentersystemer">'Opdateret d. 02-06-2026'!$A$1:$J$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Sundhedscentersystemer_excel.XLSX
+++ b/html/Sundhedscentersystemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C903D9B-5306-40A9-BC0E-9BBC67F1605D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7662E89-A513-43D6-8061-2D23712A8357}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Sundhedscentersystemer_excel.XLSX
+++ b/html/Sundhedscentersystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7662E89-A513-43D6-8061-2D23712A8357}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9E7E6DA-3275-47D3-8C83-1239A8876707}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 02-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 05-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sundhedscentersystemer">'Opdateret d. 02-06-2026'!$A$1:$J$14</definedName>
+    <definedName name="Sundhedscentersystemer">'Opdateret d. 05-06-2026'!$A$1:$J$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Sundhedscentersystemer_excel.XLSX
+++ b/html/Sundhedscentersystemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74C97CA4-9D5B-4CAB-9148-CEF82B0FBAED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{329AF655-384F-4951-8DD5-A016EC338E40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Sundhedscentersystemer_excel.XLSX
+++ b/html/Sundhedscentersystemer_excel.XLSX
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5347447E-C33D-498C-80F4-FA0484093278}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E0F2AE7-D475-4467-9611-A212561CA086}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3150" yWindow="3135" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 09-06-2026" sheetId="1" r:id="rId1"/>

--- a/html/Sundhedscentersystemer_excel.XLSX
+++ b/html/Sundhedscentersystemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E0F2AE7-D475-4467-9611-A212561CA086}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EADA21FF-E64E-42E1-B38C-9C14EA6F8B70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Sundhedscentersystemer_excel.XLSX
+++ b/html/Sundhedscentersystemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EADA21FF-E64E-42E1-B38C-9C14EA6F8B70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4645B62-29CF-4DCA-9903-48A340559E3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 09-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 15-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sundhedscentersystemer">'Opdateret d. 09-06-2026'!$A$1:$J$14</definedName>
+    <definedName name="Sundhedscentersystemer">'Opdateret d. 15-06-2026'!$A$1:$J$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -461,9 +461,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J14"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -495,7 +495,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -527,7 +527,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>15</v>
       </c>
@@ -559,7 +559,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>17</v>
       </c>
@@ -591,7 +591,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>19</v>
       </c>
@@ -623,7 +623,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>21</v>
       </c>
@@ -655,7 +655,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>24</v>
       </c>
@@ -687,7 +687,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>24</v>
       </c>
@@ -719,7 +719,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>15</v>
       </c>
@@ -751,7 +751,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>17</v>
       </c>
@@ -783,7 +783,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>28</v>
       </c>
@@ -815,7 +815,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>19</v>
       </c>
@@ -847,7 +847,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>21</v>
       </c>
@@ -879,7 +879,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>30</v>
       </c>

--- a/html/Sundhedscentersystemer_excel.XLSX
+++ b/html/Sundhedscentersystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4645B62-29CF-4DCA-9903-48A340559E3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA88EF45-A45B-4406-B936-3F9FE22819B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 15-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 22-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sundhedscentersystemer">'Opdateret d. 15-06-2026'!$A$1:$J$14</definedName>
+    <definedName name="Sundhedscentersystemer">'Opdateret d. 22-06-2026'!$A$1:$J$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Sundhedscentersystemer_excel.XLSX
+++ b/html/Sundhedscentersystemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA88EF45-A45B-4406-B936-3F9FE22819B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFF46330-7D97-4C9F-8203-A7DD664E4617}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 22-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 23-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sundhedscentersystemer">'Opdateret d. 22-06-2026'!$A$1:$J$14</definedName>
+    <definedName name="Sundhedscentersystemer">'Opdateret d. 23-06-2026'!$A$1:$J$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -461,9 +461,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J14"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -495,7 +495,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -527,7 +527,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>15</v>
       </c>
@@ -559,7 +559,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>17</v>
       </c>
@@ -591,7 +591,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>19</v>
       </c>
@@ -623,7 +623,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>21</v>
       </c>
@@ -655,7 +655,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>24</v>
       </c>
@@ -687,7 +687,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>24</v>
       </c>
@@ -719,7 +719,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>15</v>
       </c>
@@ -751,7 +751,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>17</v>
       </c>
@@ -783,7 +783,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>28</v>
       </c>
@@ -815,7 +815,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>19</v>
       </c>
@@ -847,7 +847,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>21</v>
       </c>
@@ -879,7 +879,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>30</v>
       </c>

--- a/html/Sundhedscentersystemer_excel.XLSX
+++ b/html/Sundhedscentersystemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFF46330-7D97-4C9F-8203-A7DD664E4617}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3831E08-F9A5-45DE-AC6C-3FF23A5AA7C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Sundhedscentersystemer_excel.XLSX
+++ b/html/Sundhedscentersystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA88EF45-A45B-4406-B936-3F9FE22819B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDEEC384-D100-4525-9B30-E95A4E4C94F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2304" yWindow="2304" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 22-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 23-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sundhedscentersystemer">'Opdateret d. 22-06-2026'!$A$1:$J$14</definedName>
+    <definedName name="Sundhedscentersystemer">'Opdateret d. 23-06-2026'!$A$1:$J$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Sundhedscentersystemer_excel.XLSX
+++ b/html/Sundhedscentersystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDEEC384-D100-4525-9B30-E95A4E4C94F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D5FF916-9B64-439E-9F0D-ACA8698018ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2304" yWindow="2304" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 23-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 25-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sundhedscentersystemer">'Opdateret d. 23-06-2026'!$A$1:$J$14</definedName>
+    <definedName name="Sundhedscentersystemer">'Opdateret d. 25-06-2026'!$A$1:$J$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Sundhedscentersystemer_excel.XLSX
+++ b/html/Sundhedscentersystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D5FF916-9B64-439E-9F0D-ACA8698018ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E772FAB-397E-4F9B-8000-590F3157B92A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2304" yWindow="2304" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 25-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 30-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sundhedscentersystemer">'Opdateret d. 25-06-2026'!$A$1:$J$14</definedName>
+    <definedName name="Sundhedscentersystemer">'Opdateret d. 30-06-2026'!$A$1:$J$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Sundhedscentersystemer_excel.XLSX
+++ b/html/Sundhedscentersystemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E772FAB-397E-4F9B-8000-590F3157B92A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{711F0128-0AE6-44DE-8E36-B385F583AE3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Sundhedscentersystemer_excel.XLSX
+++ b/html/Sundhedscentersystemer_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{711F0128-0AE6-44DE-8E36-B385F583AE3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDA2123F-4B8D-439A-A24A-0C0429ABD719}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 30-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 01-07-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sundhedscentersystemer">'Opdateret d. 30-06-2026'!$A$1:$J$14</definedName>
+    <definedName name="Sundhedscentersystemer">'Opdateret d. 01-07-2026'!$A$1:$J$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -461,9 +461,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J14"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -495,7 +495,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -527,7 +527,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>15</v>
       </c>
@@ -559,7 +559,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>17</v>
       </c>
@@ -591,7 +591,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>19</v>
       </c>
@@ -623,7 +623,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>21</v>
       </c>
@@ -655,7 +655,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>24</v>
       </c>
@@ -687,7 +687,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>24</v>
       </c>
@@ -719,7 +719,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>15</v>
       </c>
@@ -751,7 +751,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>17</v>
       </c>
@@ -783,7 +783,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>28</v>
       </c>
@@ -815,7 +815,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>19</v>
       </c>
@@ -847,7 +847,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>21</v>
       </c>
@@ -879,7 +879,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>30</v>
       </c>

--- a/html/Sundhedscentersystemer_excel.XLSX
+++ b/html/Sundhedscentersystemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDA2123F-4B8D-439A-A24A-0C0429ABD719}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B83577A1-3F11-4401-9507-0094782D881B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 01-07-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 02-07-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sundhedscentersystemer">'Opdateret d. 01-07-2026'!$A$1:$J$14</definedName>
+    <definedName name="Sundhedscentersystemer">'Opdateret d. 02-07-2026'!$A$1:$J$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Sundhedscentersystemer_excel.XLSX
+++ b/html/Sundhedscentersystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDA2123F-4B8D-439A-A24A-0C0429ABD719}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F43FB39-013B-411F-AC92-DB35FA3673EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 01-07-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 03-07-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sundhedscentersystemer">'Opdateret d. 01-07-2026'!$A$1:$J$14</definedName>
+    <definedName name="Sundhedscentersystemer">'Opdateret d. 03-07-2026'!$A$1:$J$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -461,9 +461,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J14"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -495,7 +495,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -527,7 +527,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>15</v>
       </c>
@@ -559,7 +559,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>17</v>
       </c>
@@ -591,7 +591,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>19</v>
       </c>
@@ -623,7 +623,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>21</v>
       </c>
@@ -655,7 +655,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>24</v>
       </c>
@@ -687,7 +687,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>24</v>
       </c>
@@ -719,7 +719,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>15</v>
       </c>
@@ -751,7 +751,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>17</v>
       </c>
@@ -783,7 +783,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>28</v>
       </c>
@@ -815,7 +815,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>19</v>
       </c>
@@ -847,7 +847,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>21</v>
       </c>
@@ -879,7 +879,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>30</v>
       </c>

--- a/html/Sundhedscentersystemer_excel.XLSX
+++ b/html/Sundhedscentersystemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B83577A1-3F11-4401-9507-0094782D881B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{225AE12A-0348-4E6B-AA60-19857BAC67E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 02-07-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 03-07-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sundhedscentersystemer">'Opdateret d. 02-07-2026'!$A$1:$J$14</definedName>
+    <definedName name="Sundhedscentersystemer">'Opdateret d. 03-07-2026'!$A$1:$J$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -461,9 +461,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J14"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -495,7 +495,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -527,7 +527,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>15</v>
       </c>
@@ -559,7 +559,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>17</v>
       </c>
@@ -591,7 +591,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>19</v>
       </c>
@@ -623,7 +623,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>21</v>
       </c>
@@ -655,7 +655,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>24</v>
       </c>
@@ -687,7 +687,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>24</v>
       </c>
@@ -719,7 +719,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>15</v>
       </c>
@@ -751,7 +751,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>17</v>
       </c>
@@ -783,7 +783,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>28</v>
       </c>
@@ -815,7 +815,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>19</v>
       </c>
@@ -847,7 +847,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>21</v>
       </c>
@@ -879,7 +879,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>30</v>
       </c>

--- a/html/Sundhedscentersystemer_excel.XLSX
+++ b/html/Sundhedscentersystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{225AE12A-0348-4E6B-AA60-19857BAC67E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DFA4078-9129-4B63-A02D-596F97DE057B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 03-07-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 09-07-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sundhedscentersystemer">'Opdateret d. 03-07-2026'!$A$1:$J$14</definedName>
+    <definedName name="Sundhedscentersystemer">'Opdateret d. 09-07-2026'!$A$1:$J$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Sundhedscentersystemer_excel.XLSX
+++ b/html/Sundhedscentersystemer_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DFA4078-9129-4B63-A02D-596F97DE057B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01C2A815-6FA3-4E3E-A45F-A7AB3C23C159}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 09-07-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 19-08-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sundhedscentersystemer">'Opdateret d. 09-07-2026'!$A$1:$J$14</definedName>
+    <definedName name="Sundhedscentersystemer">'Opdateret d. 19-08-2026'!$A$1:$J$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Sundhedscentersystemer_excel.XLSX
+++ b/html/Sundhedscentersystemer_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01C2A815-6FA3-4E3E-A45F-A7AB3C23C159}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1E37EB9-B302-4889-8DD4-0EB56BA9FAB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4560" yWindow="945" windowWidth="21600" windowHeight="12450" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 19-08-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 21-08-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sundhedscentersystemer">'Opdateret d. 19-08-2026'!$A$1:$J$14</definedName>
+    <definedName name="Sundhedscentersystemer">'Opdateret d. 21-08-2026'!$A$1:$J$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -461,9 +461,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J14"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -495,7 +495,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -527,7 +527,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>15</v>
       </c>
@@ -559,7 +559,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>17</v>
       </c>
@@ -591,7 +591,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>19</v>
       </c>
@@ -623,7 +623,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>21</v>
       </c>
@@ -655,7 +655,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>24</v>
       </c>
@@ -687,7 +687,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>24</v>
       </c>
@@ -719,7 +719,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>15</v>
       </c>
@@ -751,7 +751,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>17</v>
       </c>
@@ -783,7 +783,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>28</v>
       </c>
@@ -815,7 +815,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>19</v>
       </c>
@@ -847,7 +847,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>21</v>
       </c>
@@ -879,7 +879,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>30</v>
       </c>

--- a/html/Sundhedscentersystemer_excel.XLSX
+++ b/html/Sundhedscentersystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1E37EB9-B302-4889-8DD4-0EB56BA9FAB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F20FB5B-D1B8-41CA-B9AF-D20265D0F9BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4560" yWindow="945" windowWidth="21600" windowHeight="12450" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 21-08-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 27-08-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sundhedscentersystemer">'Opdateret d. 21-08-2026'!$A$1:$J$14</definedName>
+    <definedName name="Sundhedscentersystemer">'Opdateret d. 27-08-2026'!$A$1:$J$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -461,9 +461,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J14"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -495,7 +495,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -527,7 +527,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>15</v>
       </c>
@@ -559,7 +559,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>17</v>
       </c>
@@ -591,7 +591,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>19</v>
       </c>
@@ -623,7 +623,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>21</v>
       </c>
@@ -655,7 +655,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>24</v>
       </c>
@@ -687,7 +687,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>24</v>
       </c>
@@ -719,7 +719,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>15</v>
       </c>
@@ -751,7 +751,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>17</v>
       </c>
@@ -783,7 +783,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>28</v>
       </c>
@@ -815,7 +815,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>19</v>
       </c>
@@ -847,7 +847,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>21</v>
       </c>
@@ -879,7 +879,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>30</v>
       </c>

--- a/html/Sundhedscentersystemer_excel.XLSX
+++ b/html/Sundhedscentersystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F20FB5B-D1B8-41CA-B9AF-D20265D0F9BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBB2C111-D010-4AC5-B62C-85F1896BCE3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 27-08-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 02-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sundhedscentersystemer">'Opdateret d. 27-08-2026'!$A$1:$J$14</definedName>
+    <definedName name="Sundhedscentersystemer">'Opdateret d. 02-09-2026'!$A$1:$J$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Sundhedscentersystemer_excel.XLSX
+++ b/html/Sundhedscentersystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBB2C111-D010-4AC5-B62C-85F1896BCE3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B788201F-D7F1-4332-BF45-1B499A43BC89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14625" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 02-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 06-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sundhedscentersystemer">'Opdateret d. 02-09-2026'!$A$1:$J$14</definedName>
+    <definedName name="Sundhedscentersystemer">'Opdateret d. 06-09-2026'!$A$1:$J$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Sundhedscentersystemer_excel.XLSX
+++ b/html/Sundhedscentersystemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B788201F-D7F1-4332-BF45-1B499A43BC89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB4501FE-735F-4A2A-A051-5CF89A73C74A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14625" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Sundhedscentersystemer_excel.XLSX
+++ b/html/Sundhedscentersystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB4501FE-735F-4A2A-A051-5CF89A73C74A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB927B89-CB79-441B-9EAD-16340DA619DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14625" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 06-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 07-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sundhedscentersystemer">'Opdateret d. 06-09-2026'!$A$1:$J$14</definedName>
+    <definedName name="Sundhedscentersystemer">'Opdateret d. 07-09-2026'!$A$1:$J$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Sundhedscentersystemer_excel.XLSX
+++ b/html/Sundhedscentersystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB927B89-CB79-441B-9EAD-16340DA619DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3871D01-0138-4371-8DD9-52492DD21987}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 07-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 09-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sundhedscentersystemer">'Opdateret d. 07-09-2026'!$A$1:$J$14</definedName>
+    <definedName name="Sundhedscentersystemer">'Opdateret d. 09-09-2026'!$A$1:$J$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Sundhedscentersystemer_excel.XLSX
+++ b/html/Sundhedscentersystemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3871D01-0138-4371-8DD9-52492DD21987}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E146B522-F4C1-4A6B-950A-33AEA84A9154}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
